--- a/outputs/vcpedia-crawl/shian/shian-legend-songs-review1.xlsx
+++ b/outputs/vcpedia-crawl/shian/shian-legend-songs-review1.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="曲目数据" sheetId="1" r:id="Ra73a5544d8894251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验" sheetId="2" r:id="R5366c2cf8d324221"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="曲目数据" sheetId="1" r:id="R326f390c024e46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验" sheetId="2" r:id="R5987d904b4be4d63"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -601,7 +601,7 @@
         <x:v>45047</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
-        <x:v>诗岸</x:v>
+        <x:v>诗岸；歌爱雪</x:v>
       </x:c>
       <x:c r="F7" s="24" t="str">
         <x:v>VOCALOID；Synthesizer V</x:v>
@@ -636,7 +636,7 @@
         <x:v>45170</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str">
-        <x:v>诗岸</x:v>
+        <x:v>诗岸；歌爱雪</x:v>
       </x:c>
       <x:c r="F8" s="24" t="str">
         <x:v>VOCALOID；Synthesizer V</x:v>
@@ -1017,7 +1017,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41485a4dec9342be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfdeed893057d418b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1480,7 +1480,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78f699c6d2f14a1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b484cdb90b14176"/>
   </x:tableParts>
 </x:worksheet>
 </file>